--- a/capsule_areas.xlsx
+++ b/capsule_areas.xlsx
@@ -438,8 +438,8 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>PRG_PAR_DependenciesDistance</t>
+          <t>PRG_PAR_MeanDistToExit</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>PRG_PAR_IdealDependenciesDistance</t>
+          <t>PRG_PAR_IdealDistToExit</t>
         </is>
       </c>
     </row>
@@ -484,16 +484,16 @@
         <v>46083.69052</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>7373800</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>82.90747</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3">
@@ -503,19 +503,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>138251.07156</v>
+        <v>230418.4526</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>17512860.12962</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>211.58414</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4">
@@ -528,16 +528,16 @@
         <v>92167.38103999999</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>8664400</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>86.90747</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -550,16 +550,16 @@
         <v>397011.0276399991</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>30310741.57825989</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>244.4077011022096</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">
@@ -572,16 +572,16 @@
         <v>53766.57948000003</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>6981508.123249996</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>473.2202196913585</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7">
@@ -594,16 +594,16 @@
         <v>46083.69052</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>5530400</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>98.90747</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -616,16 +616,16 @@
         <v>59668.03606000001</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>7748160.199500005</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>94.22593113372091</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -638,10 +638,10 @@
         <v>23041.84526</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>2027800</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -660,16 +660,16 @@
         <v>115109.5048700001</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>14947468.21176</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>294.0411970632529</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11">
@@ -682,16 +682,16 @@
         <v>23041.84526</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>2534800</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>104.90747</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -701,13 +701,11 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>994224.6722099991</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>1086392.053249999</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>103631938.2423899</v>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr"/>
@@ -745,7 +743,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>994224.67221</v>
+        <v>1086392.05325</v>
       </c>
     </row>
     <row r="4">
@@ -774,7 +772,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>994224.6722099958</v>
+        <v>1086392.053249996</v>
       </c>
     </row>
     <row r="8">
@@ -803,7 +801,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>994224.6722099958</v>
+        <v>1086392.053249996</v>
       </c>
     </row>
     <row r="12">
@@ -842,7 +840,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>138251.07156</v>
+        <v>230418.4526</v>
       </c>
     </row>
     <row r="16">
@@ -951,7 +949,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>994224.6722099958</v>
+        <v>1086392.053249996</v>
       </c>
     </row>
   </sheetData>

--- a/capsule_areas.xlsx
+++ b/capsule_areas.xlsx
@@ -431,15 +431,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,15 +461,20 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>PRG_PAR_ResourceConsRatio</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>PRG_PAR_GeometryWeight</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>PRG_PAR_MeanDistToExit</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>PRG_PAR_IdealDistToExit</t>
         </is>
@@ -487,12 +493,15 @@
         <v>0.1</v>
       </c>
       <c r="D2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E2" t="n">
         <v>7373800</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>82.90747</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>75</v>
       </c>
     </row>
@@ -509,12 +518,15 @@
         <v>0.4</v>
       </c>
       <c r="D3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E3" t="n">
         <v>17512860.12962</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>211.58414</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>200</v>
       </c>
     </row>
@@ -531,12 +543,15 @@
         <v>0.15</v>
       </c>
       <c r="D4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E4" t="n">
         <v>8664400</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>86.90747</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>50</v>
       </c>
     </row>
@@ -553,12 +568,15 @@
         <v>0.16</v>
       </c>
       <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
         <v>30310741.57825989</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>244.4077011022096</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>250</v>
       </c>
     </row>
@@ -575,12 +593,15 @@
         <v>0.35</v>
       </c>
       <c r="D6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" t="n">
         <v>6981508.123249996</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>473.2202196913585</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>500</v>
       </c>
     </row>
@@ -597,12 +618,15 @@
         <v>0.3</v>
       </c>
       <c r="D7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E7" t="n">
         <v>5530400</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>98.90747</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>50</v>
       </c>
     </row>
@@ -619,12 +643,15 @@
         <v>0.5</v>
       </c>
       <c r="D8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E8" t="n">
         <v>7748160.199500005</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>94.22593113372091</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>100</v>
       </c>
     </row>
@@ -641,14 +668,17 @@
         <v>0.8</v>
       </c>
       <c r="D9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E9" t="n">
         <v>2027800</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
+      <c r="G9" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -663,12 +693,15 @@
         <v>0.25</v>
       </c>
       <c r="D10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E10" t="n">
         <v>14947468.21176</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>294.0411970632529</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>300</v>
       </c>
     </row>
@@ -685,12 +718,15 @@
         <v>0.6</v>
       </c>
       <c r="D11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E11" t="n">
         <v>2534800</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>104.90747</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>100</v>
       </c>
     </row>
@@ -704,11 +740,12 @@
         <v>1086392.053249999</v>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="n">
         <v>103631938.2423899</v>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/capsule_areas.xlsx
+++ b/capsule_areas.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet name="Program_KPI Parameters" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Version Comparison" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Data Validation" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,12 +31,17 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -47,8 +54,32 @@
         <bgColor rgb="004F81BD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E8F5"/>
+        <bgColor rgb="00D9E8F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -56,16 +87,55 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick"/>
+      <right style="thick"/>
+      <top style="thick"/>
+      <bottom style="thick"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -481,271 +551,280 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>MEP_&amp;_parking</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="2" t="n">
         <v>46083.69052</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="2" t="n">
         <v>7373800</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="2" t="n">
         <v>82.90747</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="2" t="n">
         <v>75</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>bridge</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B4" s="2" t="n">
         <v>230418.4526</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C4" s="2" t="n">
         <v>0.4</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D4" s="2" t="n">
         <v>0.3</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E4" s="2" t="n">
         <v>17512860.12962</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F4" s="2" t="n">
         <v>211.58414</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G4" s="2" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>car_parking</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B6" s="2" t="n">
         <v>92167.38103999999</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C6" s="2" t="n">
         <v>0.15</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D6" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E6" s="2" t="n">
         <v>8664400</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F6" s="2" t="n">
         <v>86.90747</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G6" s="2" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B8" s="2" t="n">
         <v>397011.0276399991</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C8" s="2" t="n">
         <v>0.16</v>
       </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="D8" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E8" s="2" t="n">
         <v>30310741.57825989</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F8" s="2" t="n">
         <v>244.4077011022096</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G8" s="2" t="n">
         <v>250</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B10" s="2" t="n">
         <v>53766.57948000003</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C10" s="2" t="n">
         <v>0.35</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D10" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E10" s="2" t="n">
         <v>6981508.123249996</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F10" s="2" t="n">
         <v>473.2202196913585</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G10" s="2" t="n">
         <v>500</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>laboratory</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>46083.69052</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E7" t="n">
-        <v>5530400</v>
-      </c>
-      <c r="F7" t="n">
-        <v>98.90747</v>
-      </c>
-      <c r="G7" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>offices</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>59668.03606000001</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E8" t="n">
-        <v>7748160.199500005</v>
-      </c>
-      <c r="F8" t="n">
-        <v>94.22593113372091</v>
-      </c>
-      <c r="G8" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>public_amenities</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>23041.84526</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2027800</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>residential</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>115109.5048700001</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E10" t="n">
-        <v>14947468.21176</v>
-      </c>
-      <c r="F10" t="n">
-        <v>294.0411970632529</v>
-      </c>
-      <c r="G10" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>sky_amenities</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>23041.84526</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2534800</v>
-      </c>
-      <c r="F11" t="n">
-        <v>104.90747</v>
-      </c>
-      <c r="G11" t="n">
-        <v>100</v>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>laboratory</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>46083.69052</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>5530400</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>98.90747</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>offices</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>59668.03606000001</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>7748160.199500005</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>94.22593113372091</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>public_amenities</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>23041.84526</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>2027800</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>residential</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>115109.5048700001</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>14947468.21176</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>294.0411970632529</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>sky_amenities</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>23041.84526</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>2534800</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>104.90747</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B21" s="4" t="n">
         <v>1086392.053249999</v>
       </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="2" t="n">
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="n">
         <v>103631938.2423899</v>
       </c>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -762,231 +841,2003 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Total Area (m2)</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="3" t="n">
         <v>1086392.05325</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Area per Tower</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Tower</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Area (m2)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="3" t="n">
         <v>1086392.053249996</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Area per Level</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Area (m2)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Unspecified</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="3" t="n">
         <v>1086392.053249996</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Area per Program</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Program</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Area (m2)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>MEP_&amp;_parking</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="3" t="n">
         <v>46083.69052</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>bridge</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="3" t="n">
         <v>230418.4526</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>car_parking</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="3" t="n">
         <v>92167.38103999999</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="3" t="n">
         <v>397011.0276399991</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" s="3" t="n">
         <v>53766.57948000003</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>laboratory</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" s="3" t="n">
         <v>46083.69052</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>offices</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="3" t="n">
         <v>59668.03606000001</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>public_amenities</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="3" t="n">
         <v>23041.84526</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>residential</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" s="3" t="n">
         <v>115109.5048700001</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>sky_amenities</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" s="3" t="n">
         <v>23041.84526</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Tower x Level Matrix (m2)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Unspecified</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" s="3" t="n">
         <v>1086392.053249996</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H69"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Program</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Previous Value</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Current Value</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>MEP_&amp;_parking</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_Area</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>46083.69052</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>MEP_&amp;_parking</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_GeometryWeight</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>7373800</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>New programs added in current version</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>MEP_&amp;_parking</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_IdealDistToExit</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>Values changed from previous version</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>MEP_&amp;_parking</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_MeanDistToExit</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>82.90747</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>Removed</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>Programs no longer in current version</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>MEP_&amp;_parking</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_ResourceConsRatio</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>MEP_&amp;_parking</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_UseRatio</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>bridge</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_Area</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>230418.4526</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>bridge</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_GeometryWeight</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>17512860.12962</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>bridge</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_IdealDistToExit</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>bridge</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_MeanDistToExit</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>211.58414</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>bridge</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_ResourceConsRatio</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>bridge</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_UseRatio</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>car_parking</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_Area</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>92167.38103999999</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>car_parking</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_GeometryWeight</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>8664400</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>car_parking</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_IdealDistToExit</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>car_parking</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_MeanDistToExit</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>86.90747</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>car_parking</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_ResourceConsRatio</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>car_parking</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_UseRatio</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_Area</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>397011.0276399991</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_GeometryWeight</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>30310741.57825989</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_IdealDistToExit</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>250</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_MeanDistToExit</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>244.4077011022096</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_ResourceConsRatio</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_UseRatio</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_Area</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>53766.57948000003</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_GeometryWeight</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>6981508.123249996</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_IdealDistToExit</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_MeanDistToExit</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>473.2202196913585</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_ResourceConsRatio</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_UseRatio</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>laboratory</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_Area</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>46083.69052</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>laboratory</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_GeometryWeight</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>5530400</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>laboratory</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_IdealDistToExit</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>laboratory</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_MeanDistToExit</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>98.90747</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>laboratory</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_ResourceConsRatio</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>laboratory</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_UseRatio</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>offices</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_Area</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>59668.03606000001</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>offices</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_GeometryWeight</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>7748160.199500005</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>offices</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_IdealDistToExit</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>offices</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_MeanDistToExit</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>94.22593113372091</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>offices</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_ResourceConsRatio</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>offices</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_UseRatio</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>public_amenities</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_Area</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>23041.84526</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>public_amenities</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_GeometryWeight</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="n">
+        <v>2027800</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>public_amenities</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_IdealDistToExit</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>public_amenities</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_ResourceConsRatio</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>public_amenities</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_UseRatio</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>residential</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_Area</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>115109.5048700001</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>residential</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_GeometryWeight</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>14947468.21176</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>residential</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_IdealDistToExit</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>residential</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_MeanDistToExit</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="n">
+        <v>294.0411970632529</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>residential</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_ResourceConsRatio</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>residential</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_UseRatio</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n"/>
+      <c r="B63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n"/>
+      <c r="E63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>sky_amenities</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_Area</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>23041.84526</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>sky_amenities</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_GeometryWeight</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="n">
+        <v>2534800</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>sky_amenities</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_IdealDistToExit</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>sky_amenities</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_MeanDistToExit</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>104.90747</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>sky_amenities</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_ResourceConsRatio</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>sky_amenities</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>PRG_PAR_UseRatio</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Data Completeness</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>Programs with data</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>Found 1715 programs with valid data</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Data Completeness</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Programs with area data</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>1/1715 programs have area &gt; 0</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>Validation check passed - data meets requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Numerical Thresholds</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Area &gt; 0 m²</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Invalid: laboratory, laboratory, car_parking</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>Validation check failed - data needs review and correction</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Numerical Thresholds</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Use Ratio (0-1)</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>All ratios valid</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Numerical Thresholds</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Resource Ratio (0-1)</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>All ratios valid</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Numerical Thresholds</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Geometry Weight &gt;= 0</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>All weights valid</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Numerical Thresholds</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Mean Distance to Exit &gt;= 0</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>All distances valid</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Numerical Thresholds</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Ideal Distance to Exit &gt;= 0</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>All distances valid</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Data Consistency</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>All KPI parameters present</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>0/1715 programs have all KPI parameters</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/capsule_areas.xlsx
+++ b/capsule_areas.xlsx
@@ -568,7 +568,7 @@
         <v>0.16</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="E5" t="n">
         <v>30310741.57825989</v>
